--- a/05_screening/calibration_screening.xlsx
+++ b/05_screening/calibration_screening.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://microsofteur-my.sharepoint.com/personal/t-vwallerich_microsoft_com/Documents/Quantum/SLR/quantum-finance-slr/05_screening/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="11_D527F4824CE2E13B04A735E928EB64038D7A9DA5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5EDE2B8-C60A-4CCC-93C2-2486EA8D9877}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="11_D527F4824CE2E13B04A735E928EB64038D7A9DA5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{355D7AD3-C5D5-477E-8F81-4C278343F62E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Screening!$A$1:$L$51</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -37,8 +40,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="290">
   <si>
     <t>Title/Abstract Screening — Instructions</t>
   </si>
@@ -172,6 +197,9 @@
     <t>openalex</t>
   </si>
   <si>
+    <t>exclude</t>
+  </si>
+  <si>
     <t>3d6d6393f792</t>
   </si>
   <si>
@@ -187,6 +215,9 @@
     <t>arxiv</t>
   </si>
   <si>
+    <t>include</t>
+  </si>
+  <si>
     <t>1760158c7e1b</t>
   </si>
   <si>
@@ -280,6 +311,9 @@
     <t>Quantum Machine Learning (QML) has shown promise in diverse applications such as environmental monitoring, healthcare diagnostics, and financial modeling. However, its practical implementation faces challenges, including limited quantum hardware and the complexity of integrating quantum algorithms with classical systems. One critical challenge is handling imbalanced datasets, where rare events are often misclassified due to skewed data distributions. Quantum Bayesian Networks (QBNs) address this issue by enhancing feature extraction and improving the classification of rare events such as oil spills. This paper introduces a Bayesian approach utilizing QBNs to classify satellite-derived imbalanced datasets, distinguishing ``oil-spill'' from ``non-spill'' regions. QBNs leverage probabilistic reasoning and quantum state preparation to integrate quantum enhancements into classical machine learning architectures. Our approach achieves a 0.99 AUC score, demonstrating its efficacy in anomaly detection and advancing precise environmental monitoring and management. While integration enhances classification performance, dataset-specific challenges require further optimization.</t>
   </si>
   <si>
+    <t>maybe</t>
+  </si>
+  <si>
     <t>31ed6a5ae697</t>
   </si>
   <si>
@@ -295,6 +329,9 @@
     <t>This thesis examines how quantum computing technology serves as a catalyst for fundamental shifts in structural power within the international system, particularly through the divergent innovation strategies of the United States and China. As quantum technologies advance toward breaking current encryption methods and enabling revolutionary capabilities in sensing and communications, the question of who controls these innovations becomes critical to understanding future power dynamics. The analysis reveals two contrasting approaches to quantum technology development. China has adopted a centralized, state-driven model, forcing its Big Tech firms to relinquish quantum research control and consolidating efforts through institutions like the Anhui Quantum Computing Engineering Research Center. This approach has enabled China to lead in quantum communications, establishing a 12,000-kilometer quantum network and launching quantum key distribution satellites. Conversely, the United States has delegated quantum innovation to private corporations, with firms like IBM, Microsoft, Amazon, and Alphabet emerging as primary developers. This market-based approach has produced advantages in quantum computing research but has simultaneously transferred unprecedented power to these corporations. Drawing on theories of technoscience rent, digital sovereignty, and structural power, this thesis argues that the U.S. delegation strategy has allowed Big Tech firms to accumulate power across all four dimensions of Susan Strange's structural power framework: security, finance, production, and knowledge. Through their control of technological infrastructure, data sovereignty, and platform power exercised via algorithmic governance, these firms now function as quasi-sovereign entities capable of constraining state foreign policy decisions. The advent of quantum computing threatens to cement this power consolidation, as firms control both the technologies necessary to break current encryption and the quantum-resistant solutions required for future security. The theoretical framework integrates concepts from quantum mechanics—particularly entanglement, uncertainty, and superposition—to reconceptualize power relationships in the international system. This quantum approach reveals how Big Tech's control over critical infrastructure creates dependencies that transcend traditional territorial sovereignty, establishing what can be termed "digital sovereignty" that operates independently of geographic boundaries. The implications are profound: states that have delegated innovation to firms face growing vulnerabilities as these corporations gain leverage over national security, economic infrastructure, and global communications. China's preemptive measures to prevent Big Tech dominance in quantum technology suggest recognition of these risks. This research contributes to international relations theory by demonstrating how technological infrastructure control by non-state actors fundamentally challenges state-centric paradigms and necessitates new frameworks for understanding power, sovereignty, and security in the quantum era.</t>
   </si>
   <si>
+    <t>Interesting, not relevant</t>
+  </si>
+  <si>
     <t>f5b1f05fe558</t>
   </si>
   <si>
@@ -370,6 +407,9 @@
     <t>Quantum computing represents a fundamentally different computational paradigm that harnesses quantum mechanical phenomena to process information in ways that classical computers cannot efficiently replicate. This paper provides an accessible introduction to quantum computing for IT professionals and developers seeking to understand the technology's principles, current state, and practical implications. The paper covers the foundational concepts of qubits, superposition, entanglement, and quantum gates, followed by an examination of prominent quantum algorithms and their applications. A comparative analysis of current quantum hardware approaches, including superconducting circuits, trapped ions, and photonic systems, contextualizes the engineering challenges that remain. The paper also addresses the implications of quantum computing for cryptography and outlines the emerging field of post-quantum cryptography. Market analysis and industry investment patterns suggest that while general-purpose quantum advantage remains years away, specific domain applications in chemistry, optimization, and financial modeling are approaching practical viability.</t>
   </si>
   <si>
+    <t>Would be helpful to develop the conceptual framework</t>
+  </si>
+  <si>
     <t>cf803ec26409</t>
   </si>
   <si>
@@ -592,6 +632,9 @@
     <t>This article explores the convergence of quantum computing and cloud computing, examining how this integration creates unprecedented opportunities for technological advancement across various sectors. It investigates the current state of quantum cloud services offered by major providers, analyzes technical implementation challenges, and evaluates the transformative potential across industries including finance, pharmaceuticals, manufacturing, transportation, and energy. By highlighting real-world applications in both commercial and non-profit contexts, the article demonstrates how quantum cloud integration democratizes access to previously inaccessible quantum resources while enhancing traditional cloud capabilities. It further examines the evolving quantum cloud ecosystem, including software development frameworks, marketplaces, education initiatives, and emerging methods for fault tolerance, illustrating how quantum-classical hybrid models represent the most promising path toward practical quantum computing implementation.</t>
   </si>
   <si>
+    <t>This could support the limitations and state of the art framing.</t>
+  </si>
+  <si>
     <t>9d465d7addba</t>
   </si>
   <si>
@@ -619,6 +662,9 @@
     <t>This chapter delves into the transformative potential of Artificial Intelligence, Quantum Computing, and Semiconductor Technology in revolutionizing industries like healthcare, finance, manufacturing, and telecommunications through a comprehensive and interdisciplinary approach. The objective is to provide a nuanced analysis of the opportunities presented by these technologies, including enhanced computational capabilities, improved efficiency, and new business models. Furthermore, the chapter addresses the significant challenges involved, including technical limitations, ethical considerations, and the need for robust regulatory frameworks. The novelty of this work lies in its integrated approach to examining the synergistic effects of AI, quantum computing, and semiconductor advancements, offering a holistic view of their combined impact on industry evolution. This chapter examines the potential, challenges, and opportunities of AI, Quantum Computing, and Semiconductor Technology to inform strategic pathways for harnessing their potential.</t>
   </si>
   <si>
+    <t>This could support the limitations and state of the art framing, though it sound over optimistic, we could raise awareness and critique.</t>
+  </si>
+  <si>
     <t>1bf880322e6f</t>
   </si>
   <si>
@@ -887,12 +933,6 @@
   </si>
   <si>
     <t>Maybe</t>
-  </si>
-  <si>
-    <t>exclude</t>
-  </si>
-  <si>
-    <t>include</t>
   </si>
 </sst>
 </file>
@@ -902,7 +942,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -988,7 +1028,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1007,6 +1047,9 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1387,153 +1430,153 @@
     <tabColor rgb="FF0078D4"/>
   </sheetPr>
   <dimension ref="A1:A32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" ht="21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1" ht="16.5">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" ht="16.5">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" ht="16.5">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" ht="16.5">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1" ht="16.5">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:1" ht="16.5">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:1" ht="16.5">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:1" ht="16.5">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:1" ht="16.5">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:1" ht="16.5">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:1" ht="16.5">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:1" ht="16.5">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:1" ht="16.5">
       <c r="A14" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:1" ht="16.5">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:1" ht="16.5">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" ht="16.5">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" ht="16.5">
       <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" ht="16.5">
       <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" ht="16.5">
       <c r="A20" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:1" ht="16.5">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:1" ht="16.5">
       <c r="A22" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" ht="16.5">
       <c r="A23" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" ht="16.5">
       <c r="A24" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" ht="16.5">
       <c r="A25" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:1" ht="16.5">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:1" ht="16.5">
       <c r="A27" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:1" ht="16.5">
       <c r="A28" s="2"/>
     </row>
-    <row r="29" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:1" ht="16.5">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:1" ht="16.5">
       <c r="A30" s="2"/>
     </row>
-    <row r="31" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:1" ht="16.5">
       <c r="A31" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:1" ht="16.5">
       <c r="A32" s="2" t="s">
         <v>24</v>
       </c>
@@ -1549,7 +1592,7 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:L51"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1557,14 +1600,14 @@
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="70" customWidth="1"/>
+    <col min="7" max="7" width="70" style="9" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="33" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="33">
       <c r="A1" s="4" t="s">
         <v>25</v>
       </c>
@@ -1602,7 +1645,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="384" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="381" customHeight="1">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1628,1520 +1671,1778 @@
         <v>43</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K2" s="5" t="str" cm="1">
+        <f t="array" ref="K2">_xlfn.IFS(AND(I2="include",J2="include"),"include", AND(I2="exclude",J2="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L2" s="5"/>
     </row>
-    <row r="3" spans="1:12" ht="176" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="159">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="5" t="str" cm="1">
+        <f t="array" ref="K3">_xlfn.IFS(AND(I3="include",J3="include"),"include", AND(I3="exclude",J3="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L3" s="5"/>
     </row>
-    <row r="4" spans="1:12" ht="192" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="173.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>48</v>
-      </c>
       <c r="I4" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="5" t="str" cm="1">
+        <f t="array" ref="K4">_xlfn.IFS(AND(I4="include",J4="include"),"include", AND(I4="exclude",J4="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="1:12" ht="176" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="159">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="5" t="str" cm="1">
+        <f t="array" ref="K5">_xlfn.IFS(AND(I5="include",J5="include"),"include", AND(I5="exclude",J5="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L5" s="5"/>
     </row>
-    <row r="6" spans="1:12" ht="80" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="102.75" customHeight="1">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" s="5" t="str" cm="1">
+        <f t="array" ref="K6">_xlfn.IFS(AND(I6="include",J6="include"),"include", AND(I6="exclude",J6="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:12" ht="32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="29.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="5" t="str" cm="1">
+        <f t="array" ref="K7">_xlfn.IFS(AND(I7="include",J7="include"),"include", AND(I7="exclude",J7="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L7" s="5"/>
     </row>
-    <row r="8" spans="1:12" ht="32" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="29.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="5" t="str" cm="1">
+        <f t="array" ref="K8">_xlfn.IFS(AND(I8="include",J8="include"),"include", AND(I8="exclude",J8="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L8" s="5"/>
     </row>
-    <row r="9" spans="1:12" ht="240" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="216.75">
       <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K9" s="5" t="str" cm="1">
+        <f t="array" ref="K9">_xlfn.IFS(AND(I9="include",J9="include"),"include", AND(I9="exclude",J9="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>maybe</v>
+      </c>
       <c r="L9" s="5"/>
     </row>
-    <row r="10" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="409.6">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-    </row>
-    <row r="11" spans="1:12" ht="144" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="5" t="str" cm="1">
+        <f t="array" ref="K10">_xlfn.IFS(AND(I10="include",J10="include"),"include", AND(I10="exclude",J10="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="130.5">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="5" t="str" cm="1">
+        <f t="array" ref="K11">_xlfn.IFS(AND(I11="include",J11="include"),"include", AND(I11="exclude",J11="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>maybe</v>
+      </c>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="409.6">
       <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" s="5" t="str" cm="1">
+        <f t="array" ref="K12">_xlfn.IFS(AND(I12="include",J12="include"),"include", AND(I12="exclude",J12="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>maybe</v>
+      </c>
       <c r="L12" s="5"/>
     </row>
-    <row r="13" spans="1:12" ht="320" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="304.5">
       <c r="A13" s="5">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" s="5" t="str" cm="1">
+        <f t="array" ref="K13">_xlfn.IFS(AND(I13="include",J13="include"),"include", AND(I13="exclude",J13="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L13" s="5"/>
     </row>
-    <row r="14" spans="1:12" ht="48" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="43.5">
       <c r="A14" s="5">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="5" t="str" cm="1">
+        <f t="array" ref="K14">_xlfn.IFS(AND(I14="include",J14="include"),"include", AND(I14="exclude",J14="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:12" ht="240" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="216.75">
       <c r="A15" s="5">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-    </row>
-    <row r="16" spans="1:12" ht="320" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" s="5" t="str" cm="1">
+        <f t="array" ref="K15">_xlfn.IFS(AND(I15="include",J15="include"),"include", AND(I15="exclude",J15="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>maybe</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="290.25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" s="5" t="str" cm="1">
+        <f t="array" ref="K16">_xlfn.IFS(AND(I16="include",J16="include"),"include", AND(I16="exclude",J16="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L16" s="5"/>
     </row>
-    <row r="17" spans="1:12" ht="176" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" ht="159">
       <c r="A17" s="5">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K17" s="5" t="str" cm="1">
+        <f t="array" ref="K17">_xlfn.IFS(AND(I17="include",J17="include"),"include", AND(I17="exclude",J17="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>maybe</v>
+      </c>
       <c r="L17" s="5"/>
     </row>
-    <row r="18" spans="1:12" ht="272" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="261">
       <c r="A18" s="5">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K18" s="5" t="str" cm="1">
+        <f t="array" ref="K18">_xlfn.IFS(AND(I18="include",J18="include"),"include", AND(I18="exclude",J18="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L18" s="5"/>
     </row>
-    <row r="19" spans="1:12" ht="320" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" ht="290.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K19" s="5" t="str" cm="1">
+        <f t="array" ref="K19">_xlfn.IFS(AND(I19="include",J19="include"),"include", AND(I19="exclude",J19="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="1:12" ht="256" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" ht="232.5">
       <c r="A20" s="5">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" s="5" t="str" cm="1">
+        <f t="array" ref="K20">_xlfn.IFS(AND(I20="include",J20="include"),"include", AND(I20="exclude",J20="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L20" s="5"/>
     </row>
-    <row r="21" spans="1:12" ht="240" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" ht="216.75">
       <c r="A21" s="5">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K21" s="5" t="str" cm="1">
+        <f t="array" ref="K21">_xlfn.IFS(AND(I21="include",J21="include"),"include", AND(I21="exclude",J21="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L21" s="5"/>
     </row>
-    <row r="22" spans="1:12" ht="48" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" ht="43.5">
       <c r="A22" s="5">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K22" s="5" t="str" cm="1">
+        <f t="array" ref="K22">_xlfn.IFS(AND(I22="include",J22="include"),"include", AND(I22="exclude",J22="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L22" s="5"/>
     </row>
-    <row r="23" spans="1:12" ht="192" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" ht="173.25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K23" s="5" t="str" cm="1">
+        <f t="array" ref="K23">_xlfn.IFS(AND(I23="include",J23="include"),"include", AND(I23="exclude",J23="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L23" s="5"/>
     </row>
-    <row r="24" spans="1:12" ht="384" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" ht="362.25">
       <c r="A24" s="5">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K24" s="5" t="str" cm="1">
+        <f t="array" ref="K24">_xlfn.IFS(AND(I24="include",J24="include"),"include", AND(I24="exclude",J24="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L24" s="5"/>
     </row>
-    <row r="25" spans="1:12" ht="304" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" ht="276">
       <c r="A25" s="5">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K25" s="5" t="str" cm="1">
+        <f t="array" ref="K25">_xlfn.IFS(AND(I25="include",J25="include"),"include", AND(I25="exclude",J25="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L25" s="5"/>
     </row>
-    <row r="26" spans="1:12" ht="256" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" ht="232.5">
       <c r="A26" s="5">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K26" s="5" t="str" cm="1">
+        <f t="array" ref="K26">_xlfn.IFS(AND(I26="include",J26="include"),"include", AND(I26="exclude",J26="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L26" s="5"/>
     </row>
-    <row r="27" spans="1:12" ht="368" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" ht="333.75">
       <c r="A27" s="5">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K27" s="5" t="str" cm="1">
+        <f t="array" ref="K27">_xlfn.IFS(AND(I27="include",J27="include"),"include", AND(I27="exclude",J27="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L27" s="5"/>
     </row>
-    <row r="28" spans="1:12" ht="48" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" ht="43.5">
       <c r="A28" s="5">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K28" s="5" t="str" cm="1">
+        <f t="array" ref="K28">_xlfn.IFS(AND(I28="include",J28="include"),"include", AND(I28="exclude",J28="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L28" s="5"/>
     </row>
-    <row r="29" spans="1:12" ht="32" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" ht="29.25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K29" s="5" t="str" cm="1">
+        <f t="array" ref="K29">_xlfn.IFS(AND(I29="include",J29="include"),"include", AND(I29="exclude",J29="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L29" s="5"/>
     </row>
-    <row r="30" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" ht="409.6">
       <c r="A30" s="5">
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K30" s="5" t="str" cm="1">
+        <f t="array" ref="K30">_xlfn.IFS(AND(I30="include",J30="include"),"include", AND(I30="exclude",J30="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L30" s="5"/>
     </row>
-    <row r="31" spans="1:12" ht="224" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" ht="202.5">
       <c r="A31" s="5">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-    </row>
-    <row r="32" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K31" s="5" t="str" cm="1">
+        <f t="array" ref="K31">_xlfn.IFS(AND(I31="include",J31="include"),"include", AND(I31="exclude",J31="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>maybe</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="409.6">
       <c r="A32" s="5">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K32" s="5" t="str" cm="1">
+        <f t="array" ref="K32">_xlfn.IFS(AND(I32="include",J32="include"),"include", AND(I32="exclude",J32="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L32" s="5"/>
     </row>
-    <row r="33" spans="1:12" ht="224" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" ht="202.5">
       <c r="A33" s="5">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-    </row>
-    <row r="34" spans="1:12" ht="384" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K33" s="5" t="str" cm="1">
+        <f t="array" ref="K33">_xlfn.IFS(AND(I33="include",J33="include"),"include", AND(I33="exclude",J33="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>maybe</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="348">
       <c r="A34" s="5">
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K34" s="5" t="str" cm="1">
+        <f t="array" ref="K34">_xlfn.IFS(AND(I34="include",J34="include"),"include", AND(I34="exclude",J34="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L34" s="5"/>
     </row>
-    <row r="35" spans="1:12" ht="288" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" ht="261">
       <c r="A35" s="5">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="5" t="str" cm="1">
+        <f t="array" ref="K35">_xlfn.IFS(AND(I35="include",J35="include"),"include", AND(I35="exclude",J35="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L35" s="5"/>
     </row>
-    <row r="36" spans="1:12" ht="384" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" ht="362.25">
       <c r="A36" s="5">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K36" s="5" t="str" cm="1">
+        <f t="array" ref="K36">_xlfn.IFS(AND(I36="include",J36="include"),"include", AND(I36="exclude",J36="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L36" s="5"/>
     </row>
-    <row r="37" spans="1:12" ht="384" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" ht="348">
       <c r="A37" s="5">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K37" s="5" t="str" cm="1">
+        <f t="array" ref="K37">_xlfn.IFS(AND(I37="include",J37="include"),"include", AND(I37="exclude",J37="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L37" s="5"/>
     </row>
-    <row r="38" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" ht="409.6">
       <c r="A38" s="5">
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K38" s="5" t="str" cm="1">
+        <f t="array" ref="K38">_xlfn.IFS(AND(I38="include",J38="include"),"include", AND(I38="exclude",J38="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L38" s="5"/>
     </row>
-    <row r="39" spans="1:12" ht="32" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" ht="29.25">
       <c r="A39" s="5">
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K39" s="5" t="str" cm="1">
+        <f t="array" ref="K39">_xlfn.IFS(AND(I39="include",J39="include"),"include", AND(I39="exclude",J39="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L39" s="5"/>
     </row>
-    <row r="40" spans="1:12" ht="192" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" ht="173.25">
       <c r="A40" s="5">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K40" s="5" t="str" cm="1">
+        <f t="array" ref="K40">_xlfn.IFS(AND(I40="include",J40="include"),"include", AND(I40="exclude",J40="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L40" s="5"/>
     </row>
-    <row r="41" spans="1:12" ht="352" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" ht="318.75">
       <c r="A41" s="5">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K41" s="5" t="str" cm="1">
+        <f t="array" ref="K41">_xlfn.IFS(AND(I41="include",J41="include"),"include", AND(I41="exclude",J41="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L41" s="5"/>
     </row>
-    <row r="42" spans="1:12" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" ht="409.6">
       <c r="A42" s="5">
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K42" s="5" t="str" cm="1">
+        <f t="array" ref="K42">_xlfn.IFS(AND(I42="include",J42="include"),"include", AND(I42="exclude",J42="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L42" s="5"/>
     </row>
-    <row r="43" spans="1:12" ht="208" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" ht="188.25">
       <c r="A43" s="5">
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K43" s="5" t="str" cm="1">
+        <f t="array" ref="K43">_xlfn.IFS(AND(I43="include",J43="include"),"include", AND(I43="exclude",J43="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L43" s="5"/>
     </row>
-    <row r="44" spans="1:12" ht="208" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" ht="202.5">
       <c r="A44" s="5">
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K44" s="5" t="str" cm="1">
+        <f t="array" ref="K44">_xlfn.IFS(AND(I44="include",J44="include"),"include", AND(I44="exclude",J44="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L44" s="5"/>
     </row>
-    <row r="45" spans="1:12" ht="32" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" ht="29.25">
       <c r="A45" s="5">
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K45" s="5" t="str" cm="1">
+        <f t="array" ref="K45">_xlfn.IFS(AND(I45="include",J45="include"),"include", AND(I45="exclude",J45="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L45" s="5"/>
     </row>
-    <row r="46" spans="1:12" ht="304" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" ht="276">
       <c r="A46" s="5">
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K46" s="5" t="str" cm="1">
+        <f t="array" ref="K46">_xlfn.IFS(AND(I46="include",J46="include"),"include", AND(I46="exclude",J46="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>exclude</v>
+      </c>
       <c r="L46" s="5"/>
     </row>
-    <row r="47" spans="1:12" ht="272" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" ht="246.75">
       <c r="A47" s="5">
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K47" s="5" t="str" cm="1">
+        <f t="array" ref="K47">_xlfn.IFS(AND(I47="include",J47="include"),"include", AND(I47="exclude",J47="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>include</v>
+      </c>
       <c r="L47" s="5"/>
     </row>
-    <row r="48" spans="1:12" ht="144" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" ht="130.5">
       <c r="A48" s="5">
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
+      <c r="J48" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K48" s="5" t="str" cm="1">
+        <f t="array" ref="K48">_xlfn.IFS(AND(I48="include",J48="include"),"include", AND(I48="exclude",J48="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>maybe</v>
+      </c>
       <c r="L48" s="5"/>
     </row>
-    <row r="49" spans="1:12" ht="48" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" ht="43.5">
       <c r="A49" s="5">
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
+      <c r="J49" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K49" s="5" t="str" cm="1">
+        <f t="array" ref="K49">_xlfn.IFS(AND(I49="include",J49="include"),"include", AND(I49="exclude",J49="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>maybe</v>
+      </c>
       <c r="L49" s="5"/>
     </row>
-    <row r="50" spans="1:12" ht="288" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" ht="261">
       <c r="A50" s="5">
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
+      <c r="J50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K50" s="5" t="str" cm="1">
+        <f t="array" ref="K50">_xlfn.IFS(AND(I50="include",J50="include"),"include", AND(I50="exclude",J50="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>maybe</v>
+      </c>
       <c r="L50" s="5"/>
     </row>
-    <row r="51" spans="1:12" ht="304" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" ht="276">
       <c r="A51" s="5">
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
+      <c r="J51" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="5" t="str" cm="1">
+        <f t="array" ref="K51">_xlfn.IFS(AND(I51="include",J51="include"),"include", AND(I51="exclude",J51="exclude"), "exclude", TRUE, "maybe")</f>
+        <v>maybe</v>
+      </c>
       <c r="L51" s="5"/>
     </row>
   </sheetData>
@@ -3194,35 +3495,35 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="16.5">
       <c r="A1" s="6" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="21" x14ac:dyDescent="0.55000000000000004">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="21">
       <c r="A2" s="3" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C2" s="8"/>
     </row>
-    <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3" ht="21">
       <c r="A3" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B3" s="7">
         <f>COUNTA(Screening!I2:I51)</f>
@@ -3233,9 +3534,9 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:3" ht="21">
       <c r="A4" s="3" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B4" s="7">
         <f>B2-B3</f>
@@ -3246,14 +3547,14 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3" ht="21">
       <c r="A5" s="2"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
     </row>
-    <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:3" ht="21">
       <c r="A6" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B6" s="7">
         <f>COUNTIF(Screening!I2:I51,"include")</f>
@@ -3264,9 +3565,9 @@
         <v>0.47826086956521741</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:3" ht="21">
       <c r="A7" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B7" s="7">
         <f>COUNTIF(Screening!I2:I51,"exclude")</f>
@@ -3277,9 +3578,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:3" ht="21">
       <c r="A8" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B8" s="7">
         <f>COUNTIF(Screening!I2:I51,"maybe")</f>
